--- a/web/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -117,7 +117,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -261,7 +261,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4815,38 +4815,30 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>56946000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>49176</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K67" s="5" t="n">
+        <v>56946000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>49176</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4885,7 +4877,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -4895,12 +4887,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -4910,12 +4902,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -4925,7 +4917,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6063,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6081,12 +6073,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -6096,12 +6088,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -6111,7 +6103,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6691,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -6709,12 +6701,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -6724,12 +6716,12 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -6739,7 +6731,7 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7381,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7399,12 +7391,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -7414,12 +7406,12 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
@@ -7429,7 +7421,7 @@
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8567,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -8585,12 +8577,12 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
@@ -8600,12 +8592,12 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
@@ -8615,7 +8607,7 @@
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24385,22 +24377,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -24485,9 +24477,9 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1225呎 (4+房)
+招标单位
 -
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -24687,17 +24679,17 @@
       <c r="L7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M7" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -24776,17 +24768,17 @@
       <c r="L8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -24865,17 +24857,17 @@
       <c r="L9" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M9" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -24954,17 +24946,17 @@
       <c r="L10" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25043,17 +25035,17 @@
       <c r="L11" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25132,17 +25124,17 @@
       <c r="L12" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
--
--
-(暂停销售)</t>
+$5695万
+$49,176/呎
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -25318,9 +25310,9 @@
       <c r="M14" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
+招标单位
 -
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25407,9 +25399,9 @@
       <c r="M15" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
+招标单位
 -
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25488,9 +25480,9 @@
       <c r="L16" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
+招标单位
 -
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -25674,9 +25666,9 @@
       <c r="M18" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
+招标单位
 -
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>11632000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>25964</v>
+        <v>23836</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>11632000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>25964</v>
+        <v>23836</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>11775000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>26283</v>
+        <v>24129</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>11775000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>26283</v>
+        <v>24129</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>11169000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>24931</v>
+        <v>22887</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>11169000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>24931</v>
+        <v>22887</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>11108000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>24795</v>
+        <v>22762</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>11108000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>24795</v>
+        <v>22762</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>11047000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>24658</v>
+        <v>22637</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>11047000</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>24658</v>
+        <v>22637</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4877,38 +4877,30 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>65412000</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>50550</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K68" s="5" t="n">
+        <v>65412000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>50550</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4917,7 +4909,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5183,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5207,7 +5199,7 @@
         <v>10830000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>24174</v>
+        <v>22193</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5218,7 +5210,7 @@
         <v>10830000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>24174</v>
+        <v>22193</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5811,7 +5803,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5827,7 +5819,7 @@
         <v>10378000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>23165</v>
+        <v>21266</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5838,7 +5830,7 @@
         <v>10378000</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>23165</v>
+        <v>21266</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -6439,7 +6431,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6455,7 +6447,7 @@
         <v>10255000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>22891</v>
+        <v>21014</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6466,7 +6458,7 @@
         <v>10255000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>22891</v>
+        <v>21014</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -7067,7 +7059,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7083,7 +7075,7 @@
         <v>9976000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>22268</v>
+        <v>20443</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7094,7 +7086,7 @@
         <v>9976000</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>22268</v>
+        <v>20443</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7695,7 +7687,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -7711,7 +7703,7 @@
         <v>9906000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>22112</v>
+        <v>20299</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -7722,7 +7714,7 @@
         <v>9906000</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>22112</v>
+        <v>20299</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -8315,7 +8307,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8331,7 +8323,7 @@
         <v>9837000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>21958</v>
+        <v>20158</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8342,7 +8334,7 @@
         <v>9837000</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>21958</v>
+        <v>20158</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -8943,7 +8935,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -8959,7 +8951,7 @@
         <v>9769000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>21806</v>
+        <v>20018</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -8970,7 +8962,7 @@
         <v>9769000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>21806</v>
+        <v>20018</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9563,7 +9555,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -9579,7 +9571,7 @@
         <v>9701000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>21654</v>
+        <v>19879</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -9590,7 +9582,7 @@
         <v>9701000</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>21654</v>
+        <v>19879</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10183,7 +10175,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10199,7 +10191,7 @@
         <v>10115000</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>22578</v>
+        <v>20727</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10210,7 +10202,7 @@
         <v>10115000</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>22578</v>
+        <v>20727</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10803,7 +10795,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -10819,7 +10811,7 @@
         <v>9567000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>21355</v>
+        <v>19605</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -10830,7 +10822,7 @@
         <v>9567000</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>21355</v>
+        <v>19605</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -24377,7 +24369,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24387,7 +24379,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>363</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24636,9 +24628,9 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1163万
-$25,964/呎
+$23,836/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -24725,9 +24717,9 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1178万
-$26,283/呎
+$24,129/呎
 (26年-02月-20日)</t>
         </is>
       </c>
@@ -24814,9 +24806,9 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1117万
-$24,931/呎
+$22,887/呎
 (26年-02月-06日)</t>
         </is>
       </c>
@@ -24903,9 +24895,9 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1111万
-$24,795/呎
+$22,762/呎
 (25年-12月-16日)</t>
         </is>
       </c>
@@ -24992,9 +24984,9 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1105万
-$24,658/呎
+$22,637/呎
 (25年-12月-10日)</t>
         </is>
       </c>
@@ -25081,9 +25073,9 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1083万
-$24,174/呎
+$22,193/呎
 (25年-11月-05日)</t>
         </is>
       </c>
@@ -25121,7 +25113,363 @@
       </c>
       <c r="J12" s="21" t="inlineStr"/>
       <c r="K12" s="21" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$6541万
+$50,550/呎
+(26年-10月-28日)</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$5695万
+$49,176/呎
+(26年-10月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1554万
+$26,429/呎
+(25年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1327万
+$26,758/呎
+(26年-02月-11日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1578万
+$26,692/呎
+(26年-02月-05日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$1038万
+$21,266/呎
+(25年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1055万
+$23,294/呎
+(25年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1299万
+$25,717/呎
+(26年-01月-23日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1302万
+$26,149/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1215万
+$24,593/呎
+(26年-01月-15日)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr"/>
+      <c r="K13" s="21" t="inlineStr"/>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$6061万
+$46,836/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$5225万
+$45,123/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1449万
+$24,643/呎
+(25年-10月-14日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1321万
+$26,639/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1570万
+$26,572/呎
+(25年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$1026万
+$21,014/呎
+(25年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1047万
+$23,108/呎
+(25年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1335万
+$26,440/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1256万
+$25,217/呎
+(25年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1197万
+$24,229/呎
+(26年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr"/>
+      <c r="K14" s="21" t="inlineStr"/>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4827万
+$37,300/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1438万
+$24,459/呎
+(25年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1315万
+$26,518/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1563万
+$26,453/呎
+(26年-01月-28日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$998万
+$20,443/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1038万
+$22,923/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1278万
+$25,309/呎
+(26年-01月-16日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1225万
+$24,594/呎
+(26年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1174万
+$23,755/呎
+(25年-10月-24日)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr"/>
+      <c r="K15" s="21" t="inlineStr"/>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$5795万
+$44,784/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1428万
+$24,277/呎
+(25年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1310万
+$26,401/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1556万
+$26,335/呎
+(26年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$991万
+$20,299/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1030万
+$22,742/呎
+(25年-10月-14日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1214万
+$24,044/呎
+(25年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1275万
+$25,608/呎
+(25年-12月-12日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1128万
+$22,830/呎
+(25年-10月-16日)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr"/>
+      <c r="K16" s="21" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
 招标单位
@@ -25129,185 +25477,185 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-$5695万
-$49,176/呎
-(26年-10月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
+$4874万
+$42,091/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 588呎 (2房)
-$1554万
-$26,429/呎
-(25年-12月-10日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+$1417万
+$24,095/呎
+(25年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 496呎 (2房)
-$1327万
-$26,758/呎
-(26年-02月-11日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$1304万
+$26,282/呎
+(25年-12月-19日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 591呎 (2房)
-$1578万
-$26,692/呎
-(26年-02月-05日)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1038万
-$23,165/呎
+$1531万
+$25,898/呎
+(25年-12月-29日)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$984万
+$20,158/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1009万
+$22,280/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1204万
+$23,851/呎
 (25年-10月-22日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1208万
+$24,253/呎
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1118万
+$22,626/呎
+(25年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr"/>
+      <c r="K17" s="21" t="inlineStr"/>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4609万
+$35,618/呎
+(25年-10月-24日)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$4029万
+$34,791/呎
+(25年-09月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1406万
+$23,918/呎
+(25年-08月-11日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1306万
+$26,323/呎
+(25年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1552万
+$26,257/呎
+(25年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 488呎 (2房)
+$977万
+$20,018/呎
+(25年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1055万
-$23,294/呎
-(25年-10月-13日)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+$1001万
+$22,104/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
-$1299万
-$25,717/呎
-(26年-01月-23日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+$1271万
+$25,160/呎
+(25年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 498呎 (2房)
-$1302万
-$26,149/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
+$1258万
+$25,253/呎
+(25年-11月-18日)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 494呎 (2房)
-$1215万
-$24,593/呎
-(26年-01月-15日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr"/>
-      <c r="K13" s="21" t="inlineStr"/>
-      <c r="L13" s="22" t="inlineStr">
+$1108万
+$22,425/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr"/>
+      <c r="K18" s="21" t="inlineStr"/>
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-$6061万
-$46,836/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="M13" s="22" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$5225万
-$45,123/呎
-(26年-06月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1449万
-$24,643/呎
-(25年-10月-14日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1321万
-$26,639/呎
-(26年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1570万
-$26,572/呎
-(25年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1026万
-$22,891/呎
-(25年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1047万
-$23,108/呎
-(25年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1335万
-$26,440/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1256万
-$25,217/呎
-(25年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1197万
-$24,229/呎
-(26年-01月-21日)</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr"/>
-      <c r="K14" s="21" t="inlineStr"/>
-      <c r="L14" s="22" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4827万
-$37,300/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
+$4917万
+$38,000/呎
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
 招标单位
@@ -25316,362 +25664,6 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1438万
-$24,459/呎
-(25年-10月-13日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1315万
-$26,518/呎
-(26年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1563万
-$26,453/呎
-(26年-01月-28日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$998万
-$22,268/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1038万
-$22,923/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1278万
-$25,309/呎
-(26年-01月-16日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1225万
-$24,594/呎
-(26年-01月-05日)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1174万
-$23,755/呎
-(25年-10月-24日)</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr"/>
-      <c r="K15" s="21" t="inlineStr"/>
-      <c r="L15" s="22" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$5795万
-$44,784/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1428万
-$24,277/呎
-(25年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1310万
-$26,401/呎
-(26年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1556万
-$26,335/呎
-(26年-01月-21日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$991万
-$22,112/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1030万
-$22,742/呎
-(25年-10月-14日)</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1214万
-$24,044/呎
-(25年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1275万
-$25,608/呎
-(25年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1128万
-$22,830/呎
-(25年-10月-16日)</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr"/>
-      <c r="K16" s="21" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M16" s="22" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$4874万
-$42,091/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1417万
-$24,095/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1304万
-$26,282/呎
-(25年-12月-19日)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1531万
-$25,898/呎
-(25年-12月-29日)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$984万
-$21,958/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1009万
-$22,280/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1204万
-$23,851/呎
-(25年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1208万
-$24,253/呎
-(25年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1118万
-$22,626/呎
-(25年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr"/>
-      <c r="K17" s="21" t="inlineStr"/>
-      <c r="L17" s="22" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4609万
-$35,618/呎
-(25年-10月-24日)</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$4029万
-$34,791/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1406万
-$23,918/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1306万
-$26,323/呎
-(25年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1552万
-$26,257/呎
-(25年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$977万
-$21,806/呎
-(25年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1001万
-$22,104/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1271万
-$25,160/呎
-(25年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1258万
-$25,253/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1108万
-$22,425/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="J18" s="21" t="inlineStr"/>
-      <c r="K18" s="21" t="inlineStr"/>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4917万
-$38,000/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
@@ -25704,9 +25696,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $970万
-$21,654/呎
+$19,879/呎
 (25年-08月-18日)</t>
         </is>
       </c>
@@ -25793,9 +25785,9 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $1012万
-$22,578/呎
+$20,727/呎
 (25年-08月-12日)</t>
         </is>
       </c>
@@ -25882,9 +25874,9 @@
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>D | 448呎 (2房)
+          <t>D | 488呎 (2房)
 $957万
-$21,355/呎
+$19,605/呎
 (25年-08月-22日)</t>
         </is>
       </c>
